--- a/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
@@ -15693,38 +15693,30 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H244" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I244" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>35496000</v>
+      </c>
+      <c r="I244" s="5" t="n">
+        <v>29000</v>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K244" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L244" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K244" s="5" t="n">
+        <v>35496000</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>29000</v>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
@@ -15733,7 +15725,7 @@
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15763,38 +15755,30 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H245" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>38263400</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>30200</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K245" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L245" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K245" s="5" t="n">
+        <v>38263400</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>30200</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -15803,7 +15787,7 @@
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35446,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35472,7 +35456,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37598,20 +37582,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
+$3826万
+$30,200/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-招标单位
--
-(在售)</t>
+$3550万
+$29,000/呎
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
@@ -17399,38 +17399,30 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="n">
+        <v>34884000</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>28500</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K271" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K271" s="5" t="n">
+        <v>34884000</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>28500</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
@@ -17439,7 +17431,7 @@
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35446,7 +35438,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35456,7 +35448,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37827,12 +37819,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-招标单位
--
-(在售)</t>
+$3488万
+$28,500/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
@@ -15698,7 +15698,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -37579,7 +37579,7 @@
           <t>A | 1267呎 (4+房)
 $3826万
 $30,200/呎
-(26年-09月-14日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -37587,7 +37587,7 @@
           <t>B | 1224呎 (4+房)
 $3550万
 $29,000/呎
-(26年-09月-14日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
@@ -17404,7 +17404,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -37824,7 +37824,7 @@
           <t>B | 1224呎 (4+房)
 $3488万
 $28,500/呎
-(26年-09月-30日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
